--- a/docs/精灵正式资产整理表.xlsx
+++ b/docs/精灵正式资产整理表.xlsx
@@ -968,7 +968,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>绿洲蜥</t>
+          <t>肖肖蜥</t>
         </is>
       </c>
       <c r="C50" s="39" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>绿洲巨蜥</t>
+          <t>肖恩蜥</t>
         </is>
       </c>
       <c r="C51" s="39" t="inlineStr">
@@ -9209,7 +9209,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart ns1:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>